--- a/output/REM_2024_P1_SECCION_D_NODRIZAS.xlsx
+++ b/output/REM_2024_P1_SECCION_D_NODRIZAS.xlsx
@@ -106,7 +106,7 @@
     <t>Centro de Salud Familiar Colina</t>
   </si>
   <si>
-    <t>Centro Comunitario de Salud Familiar Dr. José Symón Ojeda</t>
+    <t>CECOSF Haydeé Sepúlveda</t>
   </si>
   <si>
     <t>Posta de Salud Rural Las Canteras</t>
@@ -148,7 +148,7 @@
     <t>Centro Comunitario de Salud Familiar Beato Padre Hurtado</t>
   </si>
   <si>
-    <t>Hospital de Til Til</t>
+    <t>Hospital Comunitario de Til Til</t>
   </si>
   <si>
     <t>Centro de Salud Familiar Apoquindo</t>
@@ -562,7 +562,7 @@
     <t>Maipú</t>
   </si>
   <si>
-    <t>Servicio de Salud Metropolitano Sur Oriente</t>
+    <t>Servicio de Salud Metropolitano Sur - Oriente</t>
   </si>
   <si>
     <t>Servicio de Salud Metropolitano Norte</t>
